--- a/mental_health_forms/013_psychiatry_progress_note--mental_health_forms.xlsx
+++ b/mental_health_forms/013_psychiatry_progress_note--mental_health_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Session Details</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Provide date, time, and location of the session</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chief_complaint</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Chief Complaint</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the patient's chief complaint or reason for visit</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Diagnosis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Current psychiatric diagnosis</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>treatment_plan</t>
+          <t>medications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>treatment_plan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Medications</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List the patient's current medications</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medications</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Allergies</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>List the patient's allergies</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>medications</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Medical History</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>List the patient's medical history</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>vital_signs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medications</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>List the patient's vital signs (e.g., blood pressure, pulse)</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>mental_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allergies</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Mental Status</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe the patient's mental status (e.g., mood, behavior)</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical_history</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Follow-Up</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Schedule follow-up appointments</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vital_signs</t>
+          <t>signed_by</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vital_signs</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Signed By</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Provider's signature</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mental_status</t>
+          <t>follow_up_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mental_status</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Follow-up Frequency</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How often do you want to see this patient?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mental_status</t>
+          <t>signed_by_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mental_status</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Signed Date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Date of signature</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mental_status</t>
+          <t>signed_by_provider</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mental_status</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Signed By Provider</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Provider's name</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,297 +866,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>follow_up_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Follow-up Time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Follow-up time</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>signed_by</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>signed_by</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +934,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medication_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medication 1</t>
         </is>
       </c>
     </row>
@@ -1171,12 +951,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medication_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medication 2</t>
         </is>
       </c>
     </row>
@@ -1188,12 +968,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medication_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medication 3</t>
         </is>
       </c>
     </row>
@@ -1205,267 +985,114 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medication_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medication 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>medication_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Medication 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>medication_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Medication 6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mental_status_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>very_happy</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Very Happy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>mental_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>very_neutral</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Very Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
